--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487129_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487129_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0256</v>
+        <v>4.3062</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4247</v>
+        <v>5.625</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.3991</v>
+        <v>-1.3188</v>
       </c>
       <c r="G2" t="n">
         <v>2.0389</v>
@@ -610,13 +610,13 @@
         <v>4.0532</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2901</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0634</v>
+        <v>0.1369</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2267</v>
+        <v>-0.1464</v>
       </c>
       <c r="V2" t="n">
         <v>-1.7763</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1129</v>
+        <v>2.8997</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7156</v>
+        <v>1.315</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3973</v>
+        <v>1.5847</v>
       </c>
       <c r="G3" t="n">
         <v>-0.697</v>
@@ -688,13 +688,13 @@
         <v>3.0881</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1078</v>
+        <v>-0.1054</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5169</v>
+        <v>0.1164</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4092</v>
+        <v>-0.2218</v>
       </c>
       <c r="V3" t="n">
         <v>0.614</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5989</v>
+        <v>2.3183</v>
       </c>
       <c r="E4" t="n">
-        <v>5.986</v>
+        <v>5.7858</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.3871</v>
+        <v>-3.4674</v>
       </c>
       <c r="G4" t="n">
         <v>4.0486</v>
@@ -766,13 +766,13 @@
         <v>0.772</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1686</v>
+        <v>-0.112</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6359</v>
+        <v>0.4356</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4673</v>
+        <v>-0.5476</v>
       </c>
       <c r="V4" t="n">
         <v>-2.3903</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9766</v>
+        <v>2.27</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2085</v>
+        <v>2.6091</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.232</v>
+        <v>-0.339</v>
       </c>
       <c r="G5" t="n">
         <v>0.6224</v>
@@ -844,13 +844,13 @@
         <v>3.8602</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4878</v>
+        <v>-0.1943</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4336</v>
+        <v>-0.033</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0542</v>
+        <v>-0.1613</v>
       </c>
       <c r="V5" t="n">
         <v>1.842</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7866</v>
+        <v>1.4723</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1795</v>
+        <v>0.0794</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6071</v>
+        <v>1.3929</v>
       </c>
       <c r="G6" t="n">
         <v>0.3011</v>
@@ -922,13 +922,13 @@
         <v>3.0881</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5248</v>
+        <v>0.2105</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1507</v>
+        <v>-0.2508</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6755</v>
+        <v>0.4614</v>
       </c>
       <c r="V6" t="n">
         <v>-1.1623</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7134</v>
+        <v>0.9067</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9252</v>
+        <v>3.2256</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.2118</v>
+        <v>-2.3189</v>
       </c>
       <c r="G7" t="n">
         <v>3.1363</v>
@@ -1000,13 +1000,13 @@
         <v>0.579</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.546</v>
+        <v>-0.3526</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.238</v>
+        <v>0.0625</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.308</v>
+        <v>-0.4151</v>
       </c>
       <c r="V7" t="n">
         <v>-2.4559</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3453</v>
+        <v>-0.2184</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5453</v>
+        <v>0.6454</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8905999999999999</v>
+        <v>-0.8638</v>
       </c>
       <c r="G8" t="n">
         <v>-0.1106</v>
@@ -1078,13 +1078,13 @@
         <v>0.193</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4277</v>
+        <v>-0.3007</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1785</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2492</v>
+        <v>-0.2224</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. ETXEBERRIA AGUIRREZABALA</t>
+          <t>A. GORDILLO BELTRAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3885</v>
+        <v>-1.0175</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3552</v>
+        <v>0.147</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0333</v>
+        <v>-1.1646</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.741</v>
+        <v>-0.3275</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9906</v>
+        <v>-0.9201</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7504</v>
+        <v>0.5926</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4798</v>
+        <v>0.1064</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0157</v>
+        <v>-0.6262</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4641</v>
+        <v>0.7326</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2612</v>
+        <v>-0.4338</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9749</v>
+        <v>-0.2939</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2863</v>
+        <v>-0.14</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3161</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3161</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.8627</v>
+        <v>-0.4042</v>
       </c>
       <c r="T9" t="n">
-        <v>1.437</v>
+        <v>0.0407</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4257</v>
+        <v>-0.4449</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.8263</v>
+        <v>-0.2859</v>
       </c>
       <c r="W9" t="n">
-        <v>-1.3125</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5138</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. GORDILLO BELTRAN</t>
+          <t>B. ETXEBERRIA AGUIRREZABALA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1712</v>
+        <v>-1.3433</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0469</v>
+        <v>-1.2565</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2181</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3275</v>
+        <v>-1.741</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9201</v>
+        <v>-0.9906</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5926</v>
+        <v>-0.7504</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1064</v>
+        <v>-0.4798</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6262</v>
+        <v>-0.0157</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7326</v>
+        <v>-0.4641</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4338</v>
+        <v>-1.2612</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2939</v>
+        <v>-0.9749</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.14</v>
+        <v>-0.2863</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.3161</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.3161</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5579</v>
+        <v>0.9079</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0595</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4984</v>
+        <v>0.3721</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2859</v>
+        <v>-2.8263</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-1.3125</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2859</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2646</v>
+        <v>-2.1843</v>
       </c>
       <c r="E11" t="n">
         <v>-0.08</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1846</v>
+        <v>-2.1043</v>
       </c>
       <c r="G11" t="n">
         <v>-0.4519</v>
@@ -1312,13 +1312,13 @@
         <v>0.386</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4224</v>
+        <v>-0.3421</v>
       </c>
       <c r="T11" t="n">
         <v>0.1917</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6141</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-1.7763</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4842</v>
+        <v>-2.3107</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9441</v>
+        <v>-1.7438</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5401</v>
+        <v>-0.5669</v>
       </c>
       <c r="G12" t="n">
         <v>-2.629</v>
@@ -1390,13 +1390,13 @@
         <v>1.5441</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4343</v>
+        <v>-0.2607</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0278</v>
+        <v>0.2281</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.462</v>
+        <v>-0.4888</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.4645</v>
+        <v>-4.0035</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.2501</v>
+        <v>-1.9497</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2144</v>
+        <v>-2.0538</v>
       </c>
       <c r="G13" t="n">
         <v>-2.3648</v>
@@ -1468,13 +1468,13 @@
         <v>1.3511</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5864</v>
+        <v>-1.1253</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2247</v>
+        <v>0.0757</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.3616</v>
+        <v>-1.201</v>
       </c>
       <c r="V13" t="n">
         <v>0.06560000000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.095699999999998</v>
+        <v>3.0955</v>
       </c>
       <c r="E14" t="n">
         <v>14.4023</v>
       </c>
       <c r="F14" t="n">
-        <v>-11.3067</v>
+        <v>-11.3068</v>
       </c>
       <c r="G14" t="n">
         <v>1.825500000000001</v>
@@ -1522,7 +1522,7 @@
         <v>16.7764</v>
       </c>
       <c r="K14" t="n">
-        <v>6.9797</v>
+        <v>6.979700000000001</v>
       </c>
       <c r="L14" t="n">
         <v>9.796500000000002</v>
@@ -1546,13 +1546,13 @@
         <v>21.2309</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.0887</v>
+        <v>-2.0885</v>
       </c>
       <c r="T14" t="n">
-        <v>1.460900000000001</v>
+        <v>1.4613</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.5495</v>
+        <v>-3.5496</v>
       </c>
       <c r="V14" t="n">
         <v>-10.1517</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.3535</v>
+        <v>5.3593</v>
       </c>
       <c r="E15" t="n">
-        <v>7.5405</v>
+        <v>6.0384</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.187</v>
+        <v>-0.679</v>
       </c>
       <c r="G15" t="n">
         <v>2.0939</v>
@@ -1624,13 +1624,13 @@
         <v>1.5441</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9268</v>
+        <v>0.9326</v>
       </c>
       <c r="T15" t="n">
-        <v>2.5792</v>
+        <v>1.0771</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6524</v>
+        <v>-0.1445</v>
       </c>
       <c r="V15" t="n">
         <v>3.6839</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.3188</v>
+        <v>4.936</v>
       </c>
       <c r="E16" t="n">
-        <v>6.6918</v>
+        <v>5.3899</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.373</v>
+        <v>-0.454</v>
       </c>
       <c r="G16" t="n">
         <v>2.6017</v>
@@ -1702,13 +1702,13 @@
         <v>1.3511</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4119</v>
+        <v>1.0291</v>
       </c>
       <c r="T16" t="n">
-        <v>2.0306</v>
+        <v>0.7288</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3813</v>
+        <v>0.3004</v>
       </c>
       <c r="V16" t="n">
         <v>1.8842</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6526999999999999</v>
+        <v>1.2331</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8017</v>
+        <v>2.3024</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.149</v>
+        <v>-1.0693</v>
       </c>
       <c r="G17" t="n">
         <v>1.5505</v>
@@ -1780,13 +1780,13 @@
         <v>1.3511</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0774</v>
+        <v>0.503</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0317</v>
+        <v>0.469</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0457</v>
+        <v>0.034</v>
       </c>
       <c r="V17" t="n">
         <v>4.5838</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. URSU PUSCA</t>
+          <t>A. GARCIA NAVALON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1514</v>
+        <v>0.3561</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1.3913</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1514</v>
+        <v>-1.0352</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1335</v>
+        <v>0.5018</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-0.9977</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1335</v>
+        <v>1.4994</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1.3695</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.1242</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.2453</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1335</v>
+        <v>-0.8677</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-1.1219</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1335</v>
+        <v>0.2542</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.579</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.579</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0178</v>
+        <v>-0.1107</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.0218</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0178</v>
+        <v>-0.1325</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. GARCIA NAVALON</t>
+          <t>C. URSU PUSCA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0851</v>
+        <v>0.1781</v>
       </c>
       <c r="E19" t="n">
-        <v>1.191</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2761</v>
+        <v>0.1781</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5018</v>
+        <v>0.1335</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9977</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4994</v>
+        <v>0.1335</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3695</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1242</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2453</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8677</v>
+        <v>0.1335</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1219</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2542</v>
+        <v>0.1335</v>
       </c>
       <c r="P19" t="n">
-        <v>0.579</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.579</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5518999999999999</v>
+        <v>0.0446</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1785</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3735</v>
+        <v>0.0446</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6042</v>
+        <v>-0.3365</v>
       </c>
       <c r="E20" t="n">
         <v>1.0395</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6437</v>
+        <v>-1.376</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7232</v>
@@ -2014,13 +2014,13 @@
         <v>0.193</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.074</v>
+        <v>0.1937</v>
       </c>
       <c r="T20" t="n">
         <v>0.5486</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6227</v>
+        <v>-0.355</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9223</v>
+        <v>-2.8559</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3767</v>
+        <v>-2.1764</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5456</v>
+        <v>-0.6795</v>
       </c>
       <c r="G21" t="n">
         <v>0.3236</v>
@@ -2092,13 +2092,13 @@
         <v>0.386</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4911</v>
+        <v>0.5575</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1785</v>
+        <v>0.0218</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6696</v>
+        <v>0.5357</v>
       </c>
       <c r="V21" t="n">
         <v>-1.228</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.437</v>
+        <v>-3.4362</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5131</v>
+        <v>-0.5117</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.9239</v>
+        <v>-2.9246</v>
       </c>
       <c r="G22" t="n">
         <v>-2.8274</v>
@@ -2170,13 +2170,13 @@
         <v>1.5441</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8725000000000001</v>
+        <v>0.1282</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6398</v>
+        <v>0.3616</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2327</v>
+        <v>-0.2334</v>
       </c>
       <c r="V22" t="n">
         <v>0.614</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.523300000000001</v>
+        <v>-7.1944</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.068</v>
+        <v>-2.1667</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.4554</v>
+        <v>-5.0277</v>
       </c>
       <c r="G23" t="n">
         <v>-5.48</v>
@@ -2248,13 +2248,13 @@
         <v>0.772</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1832</v>
+        <v>0.1457</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5803</v>
+        <v>0.3209</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6029</v>
+        <v>-0.1752</v>
       </c>
       <c r="V23" t="n">
         <v>1.228</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.095500000000001</v>
+        <v>-1.760399999999999</v>
       </c>
       <c r="E24" t="n">
         <v>11.3067</v>
       </c>
       <c r="F24" t="n">
-        <v>-14.4023</v>
+        <v>-13.0672</v>
       </c>
       <c r="G24" t="n">
         <v>-1.8256</v>
@@ -2311,7 +2311,7 @@
         <v>-16.7763</v>
       </c>
       <c r="N24" t="n">
-        <v>-6.979799999999999</v>
+        <v>-6.979800000000001</v>
       </c>
       <c r="O24" t="n">
         <v>-9.7965</v>
@@ -2323,16 +2323,16 @@
         <v>-21.2309</v>
       </c>
       <c r="R24" t="n">
-        <v>7.7204</v>
+        <v>7.720400000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>2.0886</v>
+        <v>3.4237</v>
       </c>
       <c r="T24" t="n">
         <v>3.5496</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.4612</v>
+        <v>-0.1259</v>
       </c>
       <c r="V24" t="n">
         <v>10.1519</v>
